--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/checklist-apertura-finca-eventos-bodas.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/checklist-apertura-finca-eventos-bodas.xlsx
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>No vender fechas sin licencia</t>
+          <t>No confirmar fechas en firme sin licencia</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Si la calificación se deniega o se retrasa, hay que devolver señales. Antes de la licencia, sólo reservas con devolución íntegra pactada por escrito</t>
+          <t>Si la calificación se deniega o se retrasa, hay que devolver lo cobrado. Antes de la licencia, sólo reservas condicionadas a la licencia, con devolución íntegra si no llega, pactada por escrito (cláusula segunda bis del modelo de contrato). Al obtenerla, se convierten en firmes</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>El aforo legal lo fija la licencia. Con 300 invitados no hay plan de autoprotección estatal: empieza en 1.000 personas en edificio cerrado o carpa y en 5.000 al aire libre (Orden INT/1068/2026). Tu comunidad o tu ayuntamiento pueden pedir más</t>
+          <t>El aforo legal lo fija la licencia. Con 300 invitados no hay plan de autoprotección estatal: empieza en 1.000 personas en edificio cerrado o carpa y en 5.000 al aire libre en recinto delimitado (Orden INT/1068/2026). Tu comunidad o tu ayuntamiento pueden pedir más</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Mesas, 250 sillas y mantelería base; la decoración especial la contratan los novios</t>
+          <t>Mesas, 300 sillas y mantelería base; la decoración especial la contratan los novios</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Contrato fijo discontinuo (art. 16 del Estatuto de los Trabajadores) de marzo a noviembre, con llamamiento por escrito</t>
+          <t>Contrato fijo discontinuo (art. 16 del Estatuto de los Trabajadores) de marzo a noviembre, con llamamiento por escrito. De diciembre a febrero coordina el titular</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Un servicio de ocio con fecha concreta no tiene derecho de desistimiento (TRLGDCU, art. 103.l). Dilo en el contrato para evitar discusiones</t>
+          <t>Si contratas a distancia o fuera de la finca (web, correo o teléfono), un servicio de esparcimiento con fecha concreta queda fuera del derecho de desistimiento (TRLGDCU, art. 103.l). Dilo en el contrato para evitar discusiones</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/checklist-apertura-finca-eventos-bodas.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/checklist-apertura-finca-eventos-bodas.xlsx
@@ -951,8 +951,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1490,8 +1490,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2002,8 +2002,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2460,8 +2460,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2945,8 +2945,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -3430,8 +3430,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
